--- a/data/DEA_2000_2005.xlsx
+++ b/data/DEA_2000_2005.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amberteetsel/MSDS/DataMining/substance-abuse-predictions/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A3A156-38B3-A140-AF89-4FC075F90CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FF380D-54C2-B449-A4DA-A0EF0784BFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="640" windowWidth="27180" windowHeight="17360" xr2:uid="{BF4C633C-3937-BE41-81DD-B1704CC6752E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="57">
   <si>
     <t>Year</t>
   </si>
@@ -212,9 +212,6 @@
   </si>
   <si>
     <t>fent_gms</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -250,10 +247,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,9 +622,6 @@
       <c r="D2" s="1">
         <v>74395.72</v>
       </c>
-      <c r="E2" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -643,9 +636,6 @@
       <c r="D3" s="1">
         <v>197056.02</v>
       </c>
-      <c r="E3" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -660,9 +650,6 @@
       <c r="D4" s="1">
         <v>79671.759999999995</v>
       </c>
-      <c r="E4" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -677,9 +664,6 @@
       <c r="D5" s="1">
         <v>1569180.46</v>
       </c>
-      <c r="E5" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -694,9 +678,6 @@
       <c r="D6" s="1">
         <v>338763.08</v>
       </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -711,9 +692,6 @@
       <c r="D7" s="1">
         <v>127801</v>
       </c>
-      <c r="E7" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -728,9 +706,6 @@
       <c r="D8" s="1">
         <v>122670.29</v>
       </c>
-      <c r="E8" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -745,9 +720,6 @@
       <c r="D9" s="1">
         <v>561173.69999999995</v>
       </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -762,9 +734,6 @@
       <c r="D10" s="1">
         <v>1099714.8</v>
       </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -779,9 +748,6 @@
       <c r="D11" s="1">
         <v>469707.6</v>
       </c>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -796,9 +762,6 @@
       <c r="D12" s="1">
         <v>485477.47</v>
       </c>
-      <c r="E12" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -813,9 +776,6 @@
       <c r="D13" s="1">
         <v>327028.42</v>
       </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -830,9 +790,6 @@
       <c r="D14" s="1">
         <v>387639.97</v>
       </c>
-      <c r="E14" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -847,9 +804,6 @@
       <c r="D15" s="1">
         <v>144507.04</v>
       </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -864,11 +818,8 @@
       <c r="D16" s="1">
         <v>296328.2</v>
       </c>
-      <c r="E16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2000</v>
       </c>
@@ -881,11 +832,8 @@
       <c r="D17" s="1">
         <v>865827.59</v>
       </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2000</v>
       </c>
@@ -898,11 +846,8 @@
       <c r="D18" s="1">
         <v>45329.440000000002</v>
       </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2000</v>
       </c>
@@ -915,11 +860,8 @@
       <c r="D19" s="1">
         <v>424650.12</v>
       </c>
-      <c r="E19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2000</v>
       </c>
@@ -932,11 +874,8 @@
       <c r="D20" s="1">
         <v>546530.87</v>
       </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2000</v>
       </c>
@@ -949,11 +888,8 @@
       <c r="D21" s="1">
         <v>70460.740000000005</v>
       </c>
-      <c r="E21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2000</v>
       </c>
@@ -966,11 +902,8 @@
       <c r="D22" s="1">
         <v>299048.18</v>
       </c>
-      <c r="E22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2000</v>
       </c>
@@ -983,11 +916,8 @@
       <c r="D23" s="1">
         <v>226545.65</v>
       </c>
-      <c r="E23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2000</v>
       </c>
@@ -1000,11 +930,8 @@
       <c r="D24" s="1">
         <v>462871.57</v>
       </c>
-      <c r="E24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2000</v>
       </c>
@@ -1017,11 +944,8 @@
       <c r="D25" s="1">
         <v>536240.51</v>
       </c>
-      <c r="E25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2000</v>
       </c>
@@ -1034,11 +958,8 @@
       <c r="D26" s="1">
         <v>53283.02</v>
       </c>
-      <c r="E26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2000</v>
       </c>
@@ -1051,11 +972,8 @@
       <c r="D27" s="1">
         <v>436641.13</v>
       </c>
-      <c r="E27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2000</v>
       </c>
@@ -1068,11 +986,8 @@
       <c r="D28" s="1">
         <v>307451.33</v>
       </c>
-      <c r="E28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2000</v>
       </c>
@@ -1085,11 +1000,8 @@
       <c r="D29" s="1">
         <v>281354.59999999998</v>
       </c>
-      <c r="E29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2000</v>
       </c>
@@ -1102,11 +1014,8 @@
       <c r="D30" s="1">
         <v>230639.23</v>
       </c>
-      <c r="E30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2000</v>
       </c>
@@ -1119,11 +1028,8 @@
       <c r="D31" s="1">
         <v>299269.84999999998</v>
       </c>
-      <c r="E31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2000</v>
       </c>
@@ -1136,11 +1042,8 @@
       <c r="D32" s="1">
         <v>107260.81</v>
       </c>
-      <c r="E32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2000</v>
       </c>
@@ -1153,11 +1056,8 @@
       <c r="D33" s="1">
         <v>90607.13</v>
       </c>
-      <c r="E33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2000</v>
       </c>
@@ -1170,11 +1070,8 @@
       <c r="D34" s="1">
         <v>134806.85</v>
       </c>
-      <c r="E34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2000</v>
       </c>
@@ -1187,11 +1084,8 @@
       <c r="D35" s="1">
         <v>196512.41</v>
       </c>
-      <c r="E35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2000</v>
       </c>
@@ -1204,11 +1098,8 @@
       <c r="D36" s="1">
         <v>155251.87</v>
       </c>
-      <c r="E36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2000</v>
       </c>
@@ -1221,11 +1112,8 @@
       <c r="D37" s="1">
         <v>119400.42</v>
       </c>
-      <c r="E37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2000</v>
       </c>
@@ -1238,11 +1126,8 @@
       <c r="D38" s="1">
         <v>56929.75</v>
       </c>
-      <c r="E38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2000</v>
       </c>
@@ -1255,11 +1140,8 @@
       <c r="D39" s="1">
         <v>430032.33</v>
       </c>
-      <c r="E39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2000</v>
       </c>
@@ -1272,11 +1154,8 @@
       <c r="D40" s="1">
         <v>97055.06</v>
       </c>
-      <c r="E40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2000</v>
       </c>
@@ -1289,11 +1168,8 @@
       <c r="D41" s="1">
         <v>18900.61</v>
       </c>
-      <c r="E41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2000</v>
       </c>
@@ -1306,11 +1182,8 @@
       <c r="D42" s="1">
         <v>172331.99</v>
       </c>
-      <c r="E42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2000</v>
       </c>
@@ -1323,11 +1196,8 @@
       <c r="D43" s="1">
         <v>60840.43</v>
       </c>
-      <c r="E43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2000</v>
       </c>
@@ -1340,11 +1210,8 @@
       <c r="D44" s="1">
         <v>43789.72</v>
       </c>
-      <c r="E44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2000</v>
       </c>
@@ -1357,11 +1224,8 @@
       <c r="D45" s="1">
         <v>20082.8</v>
       </c>
-      <c r="E45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>2000</v>
       </c>
@@ -1374,11 +1238,8 @@
       <c r="D46" s="1">
         <v>22976.92</v>
       </c>
-      <c r="E46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2000</v>
       </c>
@@ -1391,11 +1252,8 @@
       <c r="D47" s="1">
         <v>534139.39</v>
       </c>
-      <c r="E47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2000</v>
       </c>
@@ -1408,9 +1266,6 @@
       <c r="D48" s="1">
         <v>78310.78</v>
       </c>
-      <c r="E48" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
@@ -1425,9 +1280,6 @@
       <c r="D49" s="1">
         <v>834318.49</v>
       </c>
-      <c r="E49" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
@@ -1442,9 +1294,6 @@
       <c r="D50" s="1">
         <v>498848.36</v>
       </c>
-      <c r="E50" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
@@ -1459,9 +1308,6 @@
       <c r="D51" s="1">
         <v>193805.29</v>
       </c>
-      <c r="E51" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
@@ -1470,10 +1316,10 @@
       <c r="B52" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52">
         <v>448472.53</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52">
         <v>415512.21</v>
       </c>
       <c r="E52">
@@ -1487,10 +1333,10 @@
       <c r="B53" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53">
         <v>1138720.6200000001</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53">
         <v>1025303.71</v>
       </c>
       <c r="E53">
@@ -1504,10 +1350,10 @@
       <c r="B54" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54">
         <v>333961.08</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54">
         <v>268516.06</v>
       </c>
       <c r="E54">
@@ -1521,10 +1367,10 @@
       <c r="B55" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55">
         <v>717418.75</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55">
         <v>422888.38</v>
       </c>
       <c r="E55">
@@ -1538,10 +1384,10 @@
       <c r="B56" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56">
         <v>798144.35</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56">
         <v>438397.23</v>
       </c>
       <c r="E56">
@@ -1555,10 +1401,10 @@
       <c r="B57" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57">
         <v>798144.35</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57">
         <v>448825.38</v>
       </c>
       <c r="E57">
@@ -1572,10 +1418,10 @@
       <c r="B58" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58">
         <v>513404.56</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58">
         <v>439740.01</v>
       </c>
       <c r="E58">
@@ -1589,10 +1435,10 @@
       <c r="B59" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59">
         <v>2570905.2999999998</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59">
         <v>810422.11</v>
       </c>
       <c r="E59">
@@ -1606,10 +1452,10 @@
       <c r="B60" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60">
         <v>1926291.19</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60">
         <v>2778340.76</v>
       </c>
       <c r="E60">
@@ -1623,10 +1469,10 @@
       <c r="B61" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61">
         <v>328541.14</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61">
         <v>299124.17</v>
       </c>
       <c r="E61">
@@ -1640,10 +1486,10 @@
       <c r="B62" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62">
         <v>349626.58</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62">
         <v>181773.27</v>
       </c>
       <c r="E62">
@@ -1657,10 +1503,10 @@
       <c r="B63" t="s">
         <v>13</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63">
         <v>478140.67</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63">
         <v>430095.72</v>
       </c>
       <c r="E63">
@@ -1674,10 +1520,10 @@
       <c r="B64" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64">
         <v>716391.6</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64">
         <v>508198.17</v>
       </c>
       <c r="E64">
@@ -1691,10 +1537,10 @@
       <c r="B65" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65">
         <v>155379.68</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65">
         <v>93803.57</v>
       </c>
       <c r="E65">
@@ -1708,10 +1554,10 @@
       <c r="B66" t="s">
         <v>16</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66">
         <v>253854.24</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66">
         <v>368230.46</v>
       </c>
       <c r="E66">
@@ -1725,10 +1571,10 @@
       <c r="B67" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67">
         <v>288720.86</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67">
         <v>259407.17</v>
       </c>
       <c r="E67">
@@ -1742,10 +1588,10 @@
       <c r="B68" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68">
         <v>347193.46</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68">
         <v>444105.05</v>
       </c>
       <c r="E68">
@@ -1759,10 +1605,10 @@
       <c r="B69" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69">
         <v>977716.67</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69">
         <v>686300.79</v>
       </c>
       <c r="E69">
@@ -1776,10 +1622,10 @@
       <c r="B70" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70">
         <v>764288.93</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70">
         <v>630253.46</v>
       </c>
       <c r="E70">
@@ -1793,10 +1639,10 @@
       <c r="B71" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71">
         <v>3121865.12</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71">
         <v>2305266.9</v>
       </c>
       <c r="E71">
@@ -1810,10 +1656,10 @@
       <c r="B72" t="s">
         <v>22</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72">
         <v>738665.42</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72">
         <v>1023038.54</v>
       </c>
       <c r="E72">
@@ -1827,10 +1673,10 @@
       <c r="B73" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73">
         <v>514630.61</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73">
         <v>1232592.6499999999</v>
       </c>
       <c r="E73">
@@ -1844,10 +1690,10 @@
       <c r="B74" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74">
         <v>85061.72</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74">
         <v>126456.86</v>
       </c>
       <c r="E74">
@@ -1861,10 +1707,10 @@
       <c r="B75" t="s">
         <v>25</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75">
         <v>400051.15</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75">
         <v>945291.39</v>
       </c>
       <c r="E75">
@@ -1878,10 +1724,10 @@
       <c r="B76" t="s">
         <v>26</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76">
         <v>478201.97</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76">
         <v>873759.52</v>
       </c>
       <c r="E76">
@@ -1895,10 +1741,10 @@
       <c r="B77" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77">
         <v>317108.81</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77">
         <v>461086.97</v>
       </c>
       <c r="E77">
@@ -1912,10 +1758,10 @@
       <c r="B78" t="s">
         <v>28</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78">
         <v>75039.5</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78">
         <v>147562.79999999999</v>
       </c>
       <c r="E78">
@@ -1929,10 +1775,10 @@
       <c r="B79" t="s">
         <v>29</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79">
         <v>38870.53</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79">
         <v>52262.11</v>
       </c>
       <c r="E79">
@@ -1946,10 +1792,10 @@
       <c r="B80" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80">
         <v>809186.84</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80">
         <v>1821028.11</v>
       </c>
       <c r="E80">
@@ -1963,10 +1809,10 @@
       <c r="B81" t="s">
         <v>31</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81">
         <v>89424.320000000007</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81">
         <v>217633.81</v>
       </c>
       <c r="E81">
@@ -1980,10 +1826,10 @@
       <c r="B82" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82">
         <v>45454.69</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82">
         <v>93481.9</v>
       </c>
       <c r="E82">
@@ -1997,10 +1843,10 @@
       <c r="B83" t="s">
         <v>33</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83">
         <v>128715.44</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83">
         <v>203819.84</v>
       </c>
       <c r="E83">
@@ -2014,10 +1860,10 @@
       <c r="B84" t="s">
         <v>34</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84">
         <v>839644.2</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84">
         <v>413302.85</v>
       </c>
       <c r="E84">
@@ -2031,10 +1877,10 @@
       <c r="B85" t="s">
         <v>35</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85">
         <v>470847.22</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85">
         <v>682687.71</v>
       </c>
       <c r="E85">
@@ -2048,10 +1894,10 @@
       <c r="B86" t="s">
         <v>36</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86">
         <v>1135773.19</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86">
         <v>1377885.47</v>
       </c>
       <c r="E86">
@@ -2065,10 +1911,10 @@
       <c r="B87" t="s">
         <v>37</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87">
         <v>752543.97</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87">
         <v>1923929.16</v>
       </c>
       <c r="E87">
@@ -2082,10 +1928,10 @@
       <c r="B88" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88">
         <v>104749.17</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88">
         <v>132588.67000000001</v>
       </c>
       <c r="E88">
@@ -2099,10 +1945,10 @@
       <c r="B89" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89">
         <v>172471.13</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89">
         <v>179909.21</v>
       </c>
       <c r="E89">
@@ -2116,10 +1962,10 @@
       <c r="B90" t="s">
         <v>40</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90">
         <v>297870.15000000002</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90">
         <v>601124.39</v>
       </c>
       <c r="E90">
@@ -2133,10 +1979,10 @@
       <c r="B91" t="s">
         <v>41</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91">
         <v>67984.98</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91">
         <v>122014.91</v>
       </c>
       <c r="E91">
@@ -2150,10 +1996,10 @@
       <c r="B92" t="s">
         <v>42</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92">
         <v>39462.42</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92">
         <v>60459.86</v>
       </c>
       <c r="E92">
@@ -2167,10 +2013,10 @@
       <c r="B93" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93">
         <v>32197.040000000001</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93">
         <v>47610.26</v>
       </c>
       <c r="E93">
@@ -2184,10 +2030,10 @@
       <c r="B94" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94">
         <v>36604.17</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94">
         <v>193461.81</v>
       </c>
       <c r="E94">
@@ -2201,10 +2047,10 @@
       <c r="B95" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95">
         <v>229310.07999999999</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95">
         <v>859184.28</v>
       </c>
       <c r="E95">
@@ -2218,10 +2064,10 @@
       <c r="B96" t="s">
         <v>46</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96">
         <v>26492.55</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96">
         <v>78643.929999999993</v>
       </c>
       <c r="E96">
@@ -2235,10 +2081,10 @@
       <c r="B97" t="s">
         <v>47</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97">
         <v>138221.88</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97">
         <v>594037.55000000005</v>
       </c>
       <c r="E97">
@@ -2252,10 +2098,10 @@
       <c r="B98" t="s">
         <v>48</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98">
         <v>48149.760000000002</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98">
         <v>188768.08</v>
       </c>
       <c r="E98">
@@ -2269,10 +2115,10 @@
       <c r="B99" t="s">
         <v>55</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99">
         <v>178566.84</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99">
         <v>383263.87</v>
       </c>
       <c r="E99">
@@ -2286,10 +2132,10 @@
       <c r="B100" t="s">
         <v>49</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100">
         <v>211689.87</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100">
         <v>969595.99</v>
       </c>
       <c r="E100">
@@ -2303,10 +2149,10 @@
       <c r="B101" t="s">
         <v>50</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101">
         <v>278374.48</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101">
         <v>1258040.3</v>
       </c>
       <c r="E101">
